--- a/Output/PowerPoint_Figures/Fig_S3/Axisless/Axis_Scaling_Reference.xlsx
+++ b/Output/PowerPoint_Figures/Fig_S3/Axisless/Axis_Scaling_Reference.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fig_S3_Axis_Info" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Fig_S3_Axis_Info" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,22 +25,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9E1F2"/>
-        <bgColor rgb="00D9E1F2"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -55,11 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,154 +413,148 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X2"/>
+  <dimension ref="A1:AB2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
-    <col width="7" customWidth="1" min="8" max="8"/>
-    <col width="7" customWidth="1" min="9" max="9"/>
-    <col width="7" customWidth="1" min="10" max="10"/>
-    <col width="7" customWidth="1" min="11" max="11"/>
-    <col width="9" customWidth="1" min="12" max="12"/>
-    <col width="9" customWidth="1" min="13" max="13"/>
-    <col width="19" customWidth="1" min="14" max="14"/>
-    <col width="20" customWidth="1" min="15" max="15"/>
-    <col width="19" customWidth="1" min="16" max="16"/>
-    <col width="20" customWidth="1" min="17" max="17"/>
-    <col width="19" customWidth="1" min="18" max="18"/>
-    <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="5" customWidth="1" min="20" max="20"/>
-    <col width="45" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
-    <col width="16" customWidth="1" min="24" max="24"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Figure</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Panel</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Filename</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>X_Label</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Y_Label</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>X_Scale</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Y_Scale</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>X_Min</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>X_Max</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Y_Min</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Y_Max</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>X_Ticks</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>X_Tick_Step</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
         <is>
           <t>Y_Ticks</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Y_Tick_Step</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Colorbar_Min</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>Colorbar_White</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>Colorbar_Max</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Colorbar_Label</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>Colorbar_Tick_Step</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
         <is>
           <t>Original_Width_in</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Original_Height_in</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Axisless_Width_in</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Axisless_Height_in</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Axisless_Width_px</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Axisless_Height_px</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>DPI</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Notes</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>Colorbar_Min</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>Colorbar_Max</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>Colorbar_Label</t>
         </is>
       </c>
     </row>
@@ -626,38 +608,49 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="N2" t="n">
-        <v>7.23</v>
+          <t>0.0, 0.2, 0.4, 0.6, 0.8, 1.0</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0.0, 0.2, 0.4, 0.6, 0.8, 1.0</t>
+        </is>
       </c>
       <c r="O2" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="P2" t="n">
-        <v>6.83</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="R2" t="n">
-        <v>4095</v>
-      </c>
-      <c r="S2" t="n">
-        <v>1153</v>
-      </c>
-      <c r="T2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="n">
+        <v>14</v>
+      </c>
+      <c r="V2" t="n">
+        <v>5</v>
+      </c>
+      <c r="W2" t="n">
+        <v>14</v>
+      </c>
+      <c r="X2" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>8400</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>3000</v>
+      </c>
+      <c r="AA2" t="n">
         <v>600</v>
       </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>3-panel scatter (Arrhythmia, Heart Damage, Concern). Models: SVM_RBF (square), XGBoost (triangle), GaussianNB (diamond). Colors: pkpd_elimination (green), dual_exponential (blue), modified_hill_hormesis (dusty rose). Diagonal y=x</t>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>3-panel scatter: Arrhythmia, Heart Damage, Concern. Models by marker: SVM_RBF (square), XGBoost (triangle), GaussianNB (diamond). Equations by color: PKPD Elimination (green), Dual Exponential (blue), Modified Hill Hormesis (dusty rose). y=x diagonal reference line.</t>
         </is>
       </c>
     </row>
